--- a/output/pdf_financials_xlsx/DLC.xlsx
+++ b/output/pdf_financials_xlsx/DLC.xlsx
@@ -4200,37 +4200,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0525</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1945</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.1945</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>15.589131</v>
       </c>
     </row>
     <row r="93">
@@ -7273,7 +7273,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -8201,7 +8205,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -10175,7 +10183,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -11102,7 +11114,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -11737,7 +11753,11 @@
           <t>Share‐based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.0525</v>
       </c>

--- a/output/pdf_financials_xlsx/DLC.xlsx
+++ b/output/pdf_financials_xlsx/DLC.xlsx
@@ -1800,37 +1800,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.188151</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001062</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.07757500000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.040474</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.055041</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.023292</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.210569</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004752</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005696</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.002361</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.037989</v>
       </c>
     </row>
     <row r="35">
@@ -1880,37 +1880,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.188151</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001062</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.07757500000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.040474</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.260154</v>
+        <v>0.315195</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.251791</v>
+        <v>0.275083</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.024376</v>
+        <v>0.234945</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.09458999999999999</v>
+        <v>0.099342</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.037248</v>
+        <v>0.042944</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.019034</v>
+        <v>0.021395</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.055685</v>
+        <v>0.09367399999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2363,34 +2363,34 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.001062</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07757500000000001</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.055041</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.023292</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.210569</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004752</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.005696</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.002361</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.682709</v>
+        <v>1.64472</v>
       </c>
     </row>
     <row r="49">
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0171</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>0.000323</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026108</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -5493,13 +5493,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0171</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>0.000323</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026108</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -19867,7 +19867,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -21153,7 +21157,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E218" s="5" t="n">
         <v>-0.0171</v>
       </c>
@@ -21650,7 +21658,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -23548,7 +23556,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -25800,7 +25808,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -27561,7 +27569,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">

--- a/output/pdf_financials_xlsx/DLC.xlsx
+++ b/output/pdf_financials_xlsx/DLC.xlsx
@@ -1222,13 +1222,13 @@
         <v>-0.192154</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.451843</v>
+        <v>-0.994061</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-5.953111</v>
+        <v>-1.668734</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.478452</v>
+        <v>-0.660215</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-4.984732</v>
@@ -1243,7 +1243,7 @@
         <v>-3.022062</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.396515</v>
+        <v>-0.279714</v>
       </c>
     </row>
     <row r="21">
@@ -5059,16 +5059,16 @@
         <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.659363</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.021834</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.115777</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -5108,10 +5108,10 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.033954</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.001606</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -5142,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.03102</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -12504,7 +12504,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -13872,7 +13876,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -14006,7 +14014,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -14292,7 +14304,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -15207,7 +15223,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -15276,7 +15296,11 @@
           <t>Acquisition of tangible assets</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -18678,7 +18702,11 @@
           <t>Purchase of marketable securities (Note 5)</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -22107,7 +22135,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -27208,7 +27240,11 @@
           <t>Income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -28084,7 +28120,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
